--- a/data/IKPA_JANUARI_2026.xlsx
+++ b/data/IKPA_JANUARI_2026.xlsx
@@ -601,19 +601,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>97.55</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -625,13 +625,13 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>90.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -640,20 +640,20 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>98.04000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>98.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,42 +669,42 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>42331120000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,27 +713,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>93.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>99.19</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -742,42 +742,42 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>73.38</v>
+        <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>99.19</v>
+        <v>100</v>
       </c>
       <c r="P3" t="n">
-        <v>94.47</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>94.47</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>2026</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -786,42 +786,42 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>40484710000</v>
+        <v>970430000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,24 +830,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>87.48</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
@@ -859,13 +859,13 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>74.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -874,27 +874,27 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>74.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>93.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2026</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,16 +903,16 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>95984080000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -921,24 +921,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,24 +947,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>91.05</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -976,7 +976,7 @@
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>64.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
@@ -991,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>92.84</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
@@ -1000,18 +1000,18 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>92.84</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2026</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>64847500000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -1093,13 +1093,13 @@
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>60.39</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1108,27 +1108,27 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>92.08</v>
+        <v>80</v>
       </c>
       <c r="Q6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>92.08</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>2026</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>574646890000</v>
+        <v>600000000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1181,24 +1181,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>67.79000000000001</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>73.56</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
         <v>80</v>
@@ -1234,18 +1234,18 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>91.95</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U7" t="n">
         <v>2026</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1254,42 +1254,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>31572500000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,24 +1298,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>86.28</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -1327,10 +1327,10 @@
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>58.85</v>
+        <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1342,27 +1342,27 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>81.77</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>90.86</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2026</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1371,42 +1371,42 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>128489370000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1420,19 +1420,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>85.92</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1444,13 +1444,13 @@
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>57.75</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
         <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9" t="n">
         <v>100</v>
@@ -1459,27 +1459,27 @@
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>81.55</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>90.61</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>2026</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>727218440000</v>
+        <v>574646890000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,24 +1532,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>80.91</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1561,13 +1561,13 @@
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>61.82</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1576,27 +1576,27 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>72.36</v>
+        <v>100</v>
       </c>
       <c r="Q10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>90.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>2026</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1605,42 +1605,42 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>5127100000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1649,24 +1649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>85.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -1678,13 +1678,13 @@
         <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>55.11</v>
+        <v>100</v>
       </c>
       <c r="L11" t="n">
         <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11" t="n">
         <v>100</v>
@@ -1693,27 +1693,27 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>81.02</v>
+        <v>100</v>
       </c>
       <c r="Q11" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>90.02</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>2026</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>139571760000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1740,24 +1740,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>79.77</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1795,7 +1795,7 @@
         <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>59.54</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1810,7 +1810,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>71.91</v>
+        <v>80</v>
       </c>
       <c r="Q12" t="n">
         <v>80</v>
@@ -1819,18 +1819,18 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>89.89</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>2026</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1839,42 +1839,42 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>10675360000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1883,24 +1883,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>79.45</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1912,13 +1912,13 @@
         <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>58.89</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
@@ -1927,27 +1927,27 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>71.78</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>89.72</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2026</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>74397990000</v>
+        <v>142639230000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1974,24 +1974,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,24 +2000,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>87.06</v>
+        <v>100</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -2029,13 +2029,13 @@
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>48.23</v>
+        <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>100</v>
@@ -2044,27 +2044,27 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>89.65000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>89.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2026</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>105914680000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>83.64</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -2146,13 +2146,13 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>50.93</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
         <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
@@ -2161,27 +2161,27 @@
         <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>80.19</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>89.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2026</v>
       </c>
       <c r="V15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>819256290000</v>
+        <v>90057130000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2208,24 +2208,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,24 +2234,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>86.34</v>
+        <v>100</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -2263,13 +2263,13 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>45.35</v>
+        <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>100</v>
@@ -2278,27 +2278,27 @@
         <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>89.06999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>89.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2026</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,16 +2307,16 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>1376500000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2325,24 +2325,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>82.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
@@ -2380,10 +2380,10 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>48.71</v>
+        <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2395,27 +2395,27 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q17" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2026</v>
       </c>
       <c r="V17" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,42 +2424,42 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>106528210000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2468,21 +2468,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
         <v>100</v>
@@ -2494,16 +2494,16 @@
         <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>88.58</v>
+        <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>65.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18" t="n">
         <v>100</v>
@@ -2512,27 +2512,27 @@
         <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>61.42</v>
+        <v>100</v>
       </c>
       <c r="Q18" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>87.75</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2026</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,16 +2541,16 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>405581540000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2559,24 +2559,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>86.45</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
         <v>100</v>
@@ -2611,16 +2611,16 @@
         <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>72.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>67.27</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
         <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
         <v>100</v>
@@ -2629,27 +2629,27 @@
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>69.39</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>86.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2026</v>
       </c>
       <c r="V19" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,42 +2658,42 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>82576290000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,24 +2702,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>72.72</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -2731,13 +2731,13 @@
         <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>45.44</v>
+        <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" t="n">
         <v>100</v>
@@ -2746,27 +2746,27 @@
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>69.09</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>86.36</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2026</v>
       </c>
       <c r="V20" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,42 +2775,42 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>38902730000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2819,24 +2819,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>94.37</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>76.84</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -2845,16 +2845,16 @@
         <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>88.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>53.67</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21" t="n">
         <v>100</v>
@@ -2863,27 +2863,27 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>69.05</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>86.31</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2026</v>
       </c>
       <c r="V21" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,42 +2892,42 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>9098870000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>71.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2965,13 +2965,13 @@
         <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>43.35</v>
+        <v>100</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
@@ -2980,27 +2980,27 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>68.67</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>85.84</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,35 +3009,35 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>43471570000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -3053,24 +3053,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>71.59999999999999</v>
+        <v>99.92</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -3082,7 +3082,7 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>43.2</v>
+        <v>99.84</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>68.64</v>
+        <v>79.97</v>
       </c>
       <c r="Q23" t="n">
         <v>80</v>
@@ -3106,18 +3106,18 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>85.8</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,35 +3126,35 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>39931940000</v>
+        <v>67124350000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
@@ -3170,24 +3170,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>69.93000000000001</v>
+        <v>99.87</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -3199,42 +3199,42 @@
         <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>39.85</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" t="n">
-        <v>100</v>
+        <v>99.75</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>67.97</v>
+        <v>99.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>84.95999999999999</v>
+        <v>99.92</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,16 +3243,16 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>40671640000</v>
+        <v>18312800000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3261,17 +3261,17 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
@@ -3287,24 +3287,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>76.11</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,10 +3316,10 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>28.33</v>
+        <v>99.63</v>
       </c>
       <c r="L25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3331,27 +3331,27 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>75.67</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>84.06999999999999</v>
+        <v>99.91</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>95645370000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3378,17 +3378,17 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>75.44</v>
+        <v>99.72</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,10 +3433,10 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>26.32</v>
+        <v>99.44</v>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3448,27 +3448,27 @@
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>75.26000000000001</v>
+        <v>79.89</v>
       </c>
       <c r="Q26" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>83.63</v>
+        <v>99.86</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,16 +3477,16 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>53136840000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3495,17 +3495,17 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
@@ -3521,24 +3521,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>440503</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>66.75</v>
+        <v>99.63</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -3550,7 +3550,7 @@
         <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>33.49</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>99.77</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>66.7</v>
+        <v>79.88</v>
       </c>
       <c r="Q27" t="n">
         <v>80</v>
@@ -3574,18 +3574,18 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>83.37</v>
+        <v>99.84</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,35 +3594,35 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>65205040000</v>
+        <v>10710500000</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEMENAG OKUS (440503)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
@@ -3638,27 +3638,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR PROV. SUMATRA SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>66.61</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
@@ -3667,42 +3667,42 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>33.22</v>
+        <v>100</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>100</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>66.64</v>
+        <v>99.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>83.31</v>
+        <v>99.67</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,35 +3711,35 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>114852670000</v>
+        <v>729500000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>90.97</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>72.81999999999999</v>
+        <v>99.48</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3781,16 +3781,16 @@
         <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>81.94</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>45.63</v>
+        <v>97.92</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
@@ -3799,27 +3799,27 @@
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>66.42</v>
+        <v>99.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>83.02</v>
+        <v>99.58</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,35 +3828,35 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>39404370000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
@@ -3872,24 +3872,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>85.83</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>75.18000000000001</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3898,45 +3898,45 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>71.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>50.35</v>
+        <v>97.28</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>65.81999999999999</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>82.27</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,35 +3945,35 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>50054370000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
@@ -3994,19 +3994,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>60.11</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -4018,7 +4018,7 @@
         <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>20.22</v>
+        <v>96.8</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>64.04000000000001</v>
+        <v>79.36</v>
       </c>
       <c r="Q31" t="n">
         <v>80</v>
@@ -4042,18 +4042,18 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>80.06</v>
+        <v>99.2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,16 +4062,16 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1001460000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -4106,24 +4106,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>100</v>
+        <v>96.92</v>
       </c>
       <c r="G32" t="n">
-        <v>59.74</v>
+        <v>99.98</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4132,10 +4132,10 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>100</v>
+        <v>93.83</v>
       </c>
       <c r="K32" t="n">
-        <v>19.48</v>
+        <v>99.95</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>63.9</v>
+        <v>79.06</v>
       </c>
       <c r="Q32" t="n">
         <v>80</v>
@@ -4159,18 +4159,18 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>79.87</v>
+        <v>98.83</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,35 +4179,35 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>3898470000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>55.76</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4252,13 +4252,13 @@
         <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>11.52</v>
+        <v>93.84</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -4267,27 +4267,27 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>62.3</v>
+        <v>98.77</v>
       </c>
       <c r="Q33" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>77.88</v>
+        <v>98.77</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,16 +4296,16 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>11480750000</v>
+        <v>14555550000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4314,17 +4314,17 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>007190</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>81.73999999999999</v>
+        <v>96.09</v>
       </c>
       <c r="G34" t="n">
-        <v>68.25</v>
+        <v>100</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,10 +4366,10 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>63.48</v>
+        <v>92.17</v>
       </c>
       <c r="K34" t="n">
-        <v>36.5</v>
+        <v>100</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>61.82</v>
+        <v>78.83</v>
       </c>
       <c r="Q34" t="n">
         <v>80</v>
@@ -4393,18 +4393,18 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>77.28</v>
+        <v>98.53</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,35 +4413,35 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>81321040000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT (007190)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>KEJARI OKUT</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -4462,19 +4462,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>440504</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>52.06</v>
+        <v>98.14</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,13 +4486,13 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>4.11</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
         <v>100</v>
@@ -4501,27 +4501,27 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>60.82</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="Q35" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>76.03</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,16 +4530,16 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>9346940000</v>
+        <v>10808640000</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -4548,17 +4548,17 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>KEMENAG OKUS (440504)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr"/>
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>007190</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>75.51000000000001</v>
+        <v>94.89</v>
       </c>
       <c r="G36" t="n">
-        <v>70.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,16 +4600,16 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>51.01</v>
+        <v>89.78</v>
       </c>
       <c r="K36" t="n">
-        <v>40.51</v>
+        <v>100</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
@@ -4618,27 +4618,27 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>60.75</v>
+        <v>98.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>75.94</v>
+        <v>98.47</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,35 +4647,35 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>9731020000</v>
+        <v>20452310000</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEJARI OKUT (007190)</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEJARI OKUT</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr"/>
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>94.28</v>
       </c>
       <c r="G37" t="n">
-        <v>50.62</v>
+        <v>100</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,16 +4717,16 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>100</v>
+        <v>88.56</v>
       </c>
       <c r="K37" t="n">
-        <v>1.23</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N37" t="n">
         <v>100</v>
@@ -4735,27 +4735,27 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>60.25</v>
+        <v>98.28</v>
       </c>
       <c r="Q37" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>75.31</v>
+        <v>98.28</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,35 +4764,35 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>5891850000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4825,7 +4825,7 @@
         <v>100</v>
       </c>
       <c r="G38" t="n">
-        <v>50.19</v>
+        <v>96.36</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4837,7 +4837,7 @@
         <v>100</v>
       </c>
       <c r="K38" t="n">
-        <v>0.37</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>60.07</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="Q38" t="n">
         <v>80</v>
@@ -4861,18 +4861,18 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>75.09</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,20 +4881,20 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>345163450000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -4930,19 +4930,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>94.25</v>
       </c>
       <c r="G39" t="n">
-        <v>50.04</v>
+        <v>99.66</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -4951,16 +4951,16 @@
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>100</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>0.07000000000000001</v>
+        <v>98.62</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
@@ -4969,27 +4969,27 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>60.01</v>
+        <v>98</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>75.02</v>
+        <v>98</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,35 +4998,35 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>475588950000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>92.62</v>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>99.47</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,45 +5068,45 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>100</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>98.41</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>60</v>
+        <v>87.47</v>
       </c>
       <c r="Q40" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>75</v>
+        <v>97.19</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,35 +5115,35 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>970430000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5159,24 +5159,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="G41" t="n">
-        <v>100</v>
+        <v>98.52</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -5185,45 +5185,45 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>100</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>99.88</v>
       </c>
       <c r="L41" t="n">
         <v>100</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>100</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="O41" t="n">
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>60</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>75</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,35 +5232,35 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>1230000000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5281,19 +5281,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>87.98</v>
+        <v>92.8</v>
       </c>
       <c r="G42" t="n">
-        <v>55.09</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,16 +5302,16 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>75.95</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>10.18</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N42" t="n">
         <v>100</v>
@@ -5320,27 +5320,27 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>58.43</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>73.04000000000001</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,16 +5349,16 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>15177700000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -5367,17 +5367,17 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5393,24 +5393,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>67.13</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>70.51000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,16 +5419,16 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>34.25</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>41.01</v>
+        <v>96.72</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
@@ -5437,27 +5437,27 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>58.34</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>72.92</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,16 +5466,16 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>31225620000</v>
+        <v>14214110000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5484,17 +5484,17 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
@@ -5510,24 +5510,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>99.92</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5536,16 +5536,16 @@
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>78.8</v>
       </c>
       <c r="K44" t="n">
-        <v>0.36</v>
+        <v>99.66</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N44" t="n">
         <v>100</v>
@@ -5554,27 +5554,27 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>50.07</v>
+        <v>96.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>71.53</v>
+        <v>96.75</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,16 +5583,16 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>15707450000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5601,17 +5601,17 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
@@ -5632,19 +5632,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>89.62</v>
       </c>
       <c r="G45" t="n">
-        <v>100</v>
+        <v>98.31</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
@@ -5653,16 +5653,16 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>79.23</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>99.91</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>93.33</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N45" t="n">
         <v>100</v>
@@ -5671,27 +5671,27 @@
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>50</v>
+        <v>96.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>71.43000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,35 +5700,35 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>1731600000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>88.25</v>
       </c>
       <c r="G46" t="n">
-        <v>100</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5770,16 +5770,16 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>98.17</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N46" t="n">
         <v>100</v>
@@ -5788,27 +5788,27 @@
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>50</v>
+        <v>96.11</v>
       </c>
       <c r="Q46" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>71.43000000000001</v>
+        <v>96.11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,35 +5817,35 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>3127760000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>95.08</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5890,13 +5890,13 @@
         <v>100</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>80.3</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N47" t="n">
         <v>100</v>
@@ -5905,27 +5905,27 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>50</v>
+        <v>96.06</v>
       </c>
       <c r="Q47" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>71.43000000000001</v>
+        <v>96.06</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,35 +5934,35 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>3484030000</v>
+        <v>38391890000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5983,16 +5983,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>88.22</v>
       </c>
       <c r="G48" t="n">
         <v>100</v>
@@ -6004,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>100</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,27 +6022,27 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>50</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>71.43000000000001</v>
+        <v>95.58</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,16 +6051,16 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>1707230000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6069,17 +6069,17 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6095,24 +6095,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>68.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,16 +6121,16 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>37.79</v>
+        <v>76.2</v>
       </c>
       <c r="K49" t="n">
-        <v>38.84</v>
+        <v>94.61</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N49" t="n">
         <v>100</v>
@@ -6139,27 +6139,27 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>48.44</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="Q49" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>69.2</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,35 +6168,35 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>29335310000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6212,71 +6212,71 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>96.73</v>
       </c>
       <c r="G50" t="n">
-        <v>55.33</v>
+        <v>95.2</v>
       </c>
       <c r="H50" t="n">
-        <v>69.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>100</v>
+        <v>93.45</v>
       </c>
       <c r="K50" t="n">
-        <v>10.66</v>
+        <v>80.81</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N50" t="n">
         <v>100</v>
       </c>
       <c r="O50" t="n">
-        <v>69.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>54.5</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="Q50" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>68.12</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,35 +6285,35 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>10808640000</v>
+        <v>37327090000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440504)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -6329,36 +6329,36 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>95.89</v>
       </c>
       <c r="G51" t="n">
-        <v>50.22</v>
+        <v>93.37</v>
       </c>
       <c r="H51" t="n">
-        <v>77.23</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
+        <v>91.78</v>
       </c>
       <c r="K51" t="n">
-        <v>0.44</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -6370,10 +6370,10 @@
         <v>100</v>
       </c>
       <c r="O51" t="n">
-        <v>77.23</v>
+        <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>54.4</v>
+        <v>76.12</v>
       </c>
       <c r="Q51" t="n">
         <v>80</v>
@@ -6382,18 +6382,18 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>67.98999999999999</v>
+        <v>95.14</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,16 +6402,16 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>317944150000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -6420,17 +6420,17 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
@@ -6451,31 +6451,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>97.44</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>69.65000000000001</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>94.88</v>
+        <v>87.36</v>
       </c>
       <c r="K52" t="n">
-        <v>39.29</v>
+        <v>87.42</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6487,10 +6487,10 @@
         <v>100</v>
       </c>
       <c r="O52" t="n">
-        <v>47.5</v>
+        <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>53.97</v>
+        <v>75.59</v>
       </c>
       <c r="Q52" t="n">
         <v>80</v>
@@ -6499,18 +6499,18 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>67.45999999999999</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,16 +6519,16 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>10710500000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -6537,17 +6537,17 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440503)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
@@ -6563,24 +6563,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>64.7</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
@@ -6589,16 +6589,16 @@
         <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>29.4</v>
+        <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>29.05</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N53" t="n">
         <v>100</v>
@@ -6607,27 +6607,27 @@
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>45.22</v>
+        <v>93.92</v>
       </c>
       <c r="Q53" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>64.59999999999999</v>
+        <v>93.92</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,16 +6636,16 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>287629890000</v>
+        <v>61767300000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -6654,17 +6654,17 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
@@ -6694,57 +6694,57 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>94.59</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>89.18000000000001</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>0.54</v>
+        <v>84.61</v>
       </c>
       <c r="L54" t="n">
         <v>100</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N54" t="n">
         <v>100</v>
       </c>
       <c r="O54" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>49.74</v>
+        <v>93.22</v>
       </c>
       <c r="Q54" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>62.17</v>
+        <v>93.22</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,12 +6753,12 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z54" t="n">
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>50.75</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>66.84999999999999</v>
+        <v>99.05</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,13 +6823,13 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>1.49</v>
+        <v>65.42</v>
       </c>
       <c r="K55" t="n">
-        <v>0.55</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6841,27 +6841,27 @@
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>55.33</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="Q55" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>61.48</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,16 +6870,16 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>6368000000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -6888,17 +6888,17 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6919,19 +6919,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>56.83</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>54.07</v>
+        <v>95.86</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
@@ -6940,16 +6940,16 @@
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>13.66</v>
+        <v>72.48</v>
       </c>
       <c r="K56" t="n">
-        <v>8.140000000000001</v>
+        <v>83.44</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N56" t="n">
         <v>100</v>
@@ -6958,27 +6958,27 @@
         <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>48.68</v>
+        <v>92.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>60.85</v>
+        <v>92.56</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,16 +6987,16 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>16133240000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -7005,17 +7005,17 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7036,22 +7036,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>84.53</v>
       </c>
       <c r="H57" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
         <v>100</v>
@@ -7060,7 +7060,7 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>0.33</v>
+        <v>69.05</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7072,30 +7072,30 @@
         <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>41.32</v>
+        <v>73.81</v>
       </c>
       <c r="Q57" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>59.02</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,35 +7104,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>7585360000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,31 +7153,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>85.63</v>
       </c>
       <c r="G58" t="n">
-        <v>51.36</v>
+        <v>94.89</v>
       </c>
       <c r="H58" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>2.71</v>
+        <v>89.77</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -7189,10 +7189,10 @@
         <v>100</v>
       </c>
       <c r="O58" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>46.54</v>
+        <v>73.64</v>
       </c>
       <c r="Q58" t="n">
         <v>80</v>
@@ -7201,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>58.18</v>
+        <v>92.05</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,16 +7221,16 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>7789580000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -7239,17 +7239,17 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7265,71 +7265,71 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>67.01000000000001</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>56.22</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>67.94</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>34.02</v>
+        <v>89.36</v>
       </c>
       <c r="K59" t="n">
-        <v>12.43</v>
+        <v>67.84</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N59" t="n">
         <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>67.94</v>
+        <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>44.57</v>
+        <v>91.97</v>
       </c>
       <c r="Q59" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>55.72</v>
+        <v>91.97</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,35 +7338,35 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>5176090000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7382,71 +7382,71 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>84.84</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>69.67</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>77.98</v>
       </c>
       <c r="L60" t="n">
         <v>100</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N60" t="n">
-        <v>100</v>
+        <v>99.72</v>
       </c>
       <c r="O60" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>42.5</v>
+        <v>91.02</v>
       </c>
       <c r="Q60" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>53.13</v>
+        <v>91.02</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>729500000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7504,34 +7504,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>80.69</v>
+        <v>79.63</v>
       </c>
       <c r="G61" t="n">
-        <v>68.29000000000001</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>61.37</v>
+        <v>59.26</v>
       </c>
       <c r="K61" t="n">
-        <v>4.86</v>
+        <v>86.69</v>
       </c>
       <c r="L61" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -7540,30 +7540,30 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="P61" t="n">
-        <v>47.68</v>
+        <v>71.23</v>
       </c>
       <c r="Q61" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>52.98</v>
+        <v>89.03</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,35 +7572,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>20589110000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7621,31 +7621,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>54.04</v>
+        <v>71.36</v>
       </c>
       <c r="G62" t="n">
-        <v>51.27</v>
+        <v>99.48</v>
       </c>
       <c r="H62" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>8.07</v>
+        <v>42.72</v>
       </c>
       <c r="K62" t="n">
-        <v>2.53</v>
+        <v>98.95</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -7657,10 +7657,10 @@
         <v>100</v>
       </c>
       <c r="O62" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P62" t="n">
-        <v>37.97</v>
+        <v>71.2</v>
       </c>
       <c r="Q62" t="n">
         <v>80</v>
@@ -7669,18 +7669,18 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>47.46</v>
+        <v>89</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,35 +7689,35 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>5671610000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7733,71 +7733,71 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>695176</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>50.65</v>
+        <v>72.23</v>
       </c>
       <c r="G63" t="n">
-        <v>100</v>
+        <v>96.34</v>
       </c>
       <c r="H63" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>1.29</v>
+        <v>44.45</v>
       </c>
       <c r="K63" t="n">
-        <v>0.57</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N63" t="n">
         <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P63" t="n">
-        <v>26.56</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="Q63" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>37.94</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,35 +7806,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>13489830000</v>
+        <v>6728240000</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>KANTOR KEMENHAJ OKU</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>KANTOR KEMENHAJ OKU (695176)</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>KANTOR KEMENHAJ OKU</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr"/>
@@ -7855,66 +7855,66 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>50.34</v>
+        <v>79.62</v>
       </c>
       <c r="G64" t="n">
-        <v>50.17</v>
+        <v>90.36</v>
       </c>
       <c r="H64" t="n">
-        <v>30.46</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>0.68</v>
+        <v>59.23</v>
       </c>
       <c r="K64" t="n">
-        <v>0.33</v>
+        <v>81.44</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N64" t="n">
         <v>100</v>
       </c>
       <c r="O64" t="n">
-        <v>30.46</v>
+        <v>100</v>
       </c>
       <c r="P64" t="n">
-        <v>27.78</v>
+        <v>88.17</v>
       </c>
       <c r="Q64" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>34.73</v>
+        <v>88.17</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,16 +7923,16 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>4481070000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7972,66 +7972,66 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>50</v>
+        <v>76.69</v>
       </c>
       <c r="G65" t="n">
-        <v>100</v>
+        <v>92.92</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>53.38</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N65" t="n">
         <v>100</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>87.34</v>
       </c>
       <c r="Q65" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>14.29</v>
+        <v>87.34</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,16 +8040,16 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6722660000</v>
+        <v>6314270000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN (695184)</t>
+          <t>KANTOR KEMENHAJ OKUT (695182)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,66 +8089,66 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695176</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>50</v>
+        <v>75.98</v>
       </c>
       <c r="G66" t="n">
-        <v>100</v>
+        <v>88.78</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>51.95</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="N66" t="n">
         <v>100</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P66" t="n">
-        <v>10</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="Q66" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>14.29</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,16 +8157,16 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6728240000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU (695176)</t>
+          <t>KANTOR KEMENHAJ OKUS (695184)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8201,39 +8201,39 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>50</v>
+        <v>79.72</v>
       </c>
       <c r="G67" t="n">
-        <v>100</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
         <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>59.43</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>91.58</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -8242,30 +8242,30 @@
         <v>100</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P67" t="n">
-        <v>10</v>
+        <v>82.23</v>
       </c>
       <c r="Q67" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>14.29</v>
+        <v>82.23</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>JANUARI</t>
+          <t>JUNI</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2026</v>
       </c>
       <c r="V67" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,35 +8274,35 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>JANUARI 2026</t>
+          <t>JUNI 2026</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>6314270000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR (695182)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>

--- a/data/IKPA_JANUARI_2026.xlsx
+++ b/data/IKPA_JANUARI_2026.xlsx
@@ -601,19 +601,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>099228</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>97.55</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -625,13 +625,13 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
@@ -640,20 +640,20 @@
         <v>100</v>
       </c>
       <c r="P2" t="n">
-        <v>80</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -669,42 +669,42 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>5127100000</v>
+        <v>42331120000</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>PN BATURAJA (099228)</t>
+          <t>PA BATURAJA (402267)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -713,27 +713,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>440506</t>
+          <t>401945</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>99.19</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -742,42 +742,42 @@
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>73.38</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N3" t="n">
         <v>100</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
+        <v>99.19</v>
       </c>
       <c r="P3" t="n">
-        <v>80</v>
+        <v>94.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>94.47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U3" t="n">
         <v>2026</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -786,42 +786,42 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>970430000</v>
+        <v>40484710000</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440506)</t>
+          <t>PA MUARADUA (401945)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>PA MUARADUA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,24 +830,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>692340</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MARTAPURA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>87.48</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
@@ -859,13 +859,13 @@
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>100</v>
@@ -874,27 +874,27 @@
         <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>100</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>2026</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,42 +903,42 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>139571760000</v>
+        <v>18312800000</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA (692340)</t>
+          <t>KEJARI  OKU (007130)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>LAPAS MARTAPURA</t>
+          <t>KEJARI  OKU</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -947,24 +947,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>91.05</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -976,7 +976,7 @@
         <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
@@ -991,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>92.84</v>
       </c>
       <c r="Q5" t="n">
         <v>100</v>
@@ -1000,18 +1000,18 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>92.84</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>2026</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>106528210000</v>
+        <v>64847500000</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA (692339)</t>
+          <t>PA MARTAPURA (401944)</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>RUTAN BATURAJA</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1064,24 +1064,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>666505</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
@@ -1093,13 +1093,13 @@
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>60.39</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
         <v>100</v>
@@ -1108,27 +1108,27 @@
         <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>80</v>
+        <v>92.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>92.08</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>2026</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>600000000</v>
+        <v>574646890000</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666505)</t>
+          <t>POLRES OKUS (665307)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>POLRES OKUS</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1181,24 +1181,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>666504</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>100</v>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         <v>100</v>
       </c>
       <c r="P7" t="n">
-        <v>80</v>
+        <v>73.56</v>
       </c>
       <c r="Q7" t="n">
         <v>80</v>
@@ -1234,18 +1234,18 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>91.95</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U7" t="n">
         <v>2026</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1254,42 +1254,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>3127760000</v>
+        <v>31572500000</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666504)</t>
+          <t>BAPAS OKU INDUK (692625)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BAPAS OKU INDUK</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1298,24 +1298,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>86.28</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -1327,10 +1327,10 @@
         <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>58.85</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1342,27 +1342,27 @@
         <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>80</v>
+        <v>81.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>90.86</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U8" t="n">
         <v>2026</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1371,42 +1371,42 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>31572500000</v>
+        <v>128489370000</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK (692625)</t>
+          <t>PN BATURAJA (098963)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>BAPAS OKU INDUK</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1420,19 +1420,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>85.5</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -1444,42 +1444,42 @@
         <v>100</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>57.75</v>
       </c>
       <c r="L9" t="n">
         <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>100</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>100</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>81.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>90.47</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U9" t="n">
         <v>2026</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>574646890000</v>
+        <v>727218440000</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>POLRES OKUS (665307)</t>
+          <t>POLRES OKU (641681)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>POLRES OKUS</t>
+          <t>POLRES OKU</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1532,24 +1532,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>099228</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>80.91</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -1561,13 +1561,13 @@
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>61.82</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>100</v>
@@ -1576,27 +1576,27 @@
         <v>100</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>72.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U10" t="n">
         <v>2026</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1605,42 +1605,42 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>819256290000</v>
+        <v>5127100000</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>POLRES OKUT (665292)</t>
+          <t>PN BATURAJA (099228)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>POLRES OKUT</t>
+          <t>PN BATURAJA</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1649,24 +1649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>LAPAS KELAS II B MARTAPURA</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -1678,13 +1678,13 @@
         <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>55.11</v>
       </c>
       <c r="L11" t="n">
         <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>100</v>
@@ -1693,27 +1693,27 @@
         <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>81.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>90.02</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U11" t="n">
         <v>2026</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>727218440000</v>
+        <v>139571760000</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1740,24 +1740,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>POLRES OKU (641681)</t>
+          <t>LAPAS MARTAPURA (692340)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>POLRES OKU</t>
+          <t>LAPAS MARTAPURA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,24 +1766,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>066</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>79.77</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1795,7 +1795,7 @@
         <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>59.54</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1810,7 +1810,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>80</v>
+        <v>71.91</v>
       </c>
       <c r="Q12" t="n">
         <v>80</v>
@@ -1819,18 +1819,18 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>89.89</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>2026</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1839,42 +1839,42 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>11480750000</v>
+        <v>10675360000</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA (527975)</t>
+          <t>BNN OKUT (111079)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>KPPN BATURAJA</t>
+          <t>BNN OKUT</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1883,24 +1883,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>666501</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>79.45</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1912,13 +1912,13 @@
         <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>58.89</v>
       </c>
       <c r="L13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>100</v>
@@ -1927,27 +1927,27 @@
         <v>100</v>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>71.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>89.72</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>2026</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>142639230000</v>
+        <v>74397990000</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1974,24 +1974,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666501)</t>
+          <t>BPN OKU (431142)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPN OKU</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2000,24 +2000,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>440505</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>87.06</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -2029,13 +2029,13 @@
         <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>48.23</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
         <v>100</v>
@@ -2044,27 +2044,27 @@
         <v>100</v>
       </c>
       <c r="P14" t="n">
-        <v>80</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U14" t="n">
         <v>2026</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>1001460000</v>
+        <v>105914680000</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440505)</t>
+          <t>LAPAS MUARA DUA (692334)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>LAPAS MUARA DUA</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2117,24 +2117,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>060</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>440502</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>100</v>
+        <v>83.64</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -2146,13 +2146,13 @@
         <v>100</v>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>50.93</v>
       </c>
       <c r="L15" t="n">
         <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>100</v>
@@ -2161,27 +2161,27 @@
         <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>80.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U15" t="n">
         <v>2026</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>90057130000</v>
+        <v>819256290000</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2208,24 +2208,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS (440502)</t>
+          <t>POLRES OKUT (665292)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>KEMENAG OKUS</t>
+          <t>POLRES OKUT</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2234,24 +2234,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>418462</t>
+          <t>403409</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>100</v>
+        <v>86.34</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -2263,13 +2263,13 @@
         <v>100</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>45.35</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16" t="n">
         <v>100</v>
@@ -2278,27 +2278,27 @@
         <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>80</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U16" t="n">
         <v>2026</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2307,16 +2307,16 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>5891850000</v>
+        <v>1376500000</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2325,24 +2325,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS (418462)</t>
+          <t>PA MARTAPURA (403409)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUS</t>
+          <t>PA MARTAPURA</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>669055</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>100</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
@@ -2380,7 +2380,7 @@
         <v>100</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>56.19</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2395,7 +2395,7 @@
         <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>80</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="Q17" t="n">
         <v>80</v>
@@ -2404,18 +2404,18 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>89.05</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U17" t="n">
         <v>2026</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2424,42 +2424,42 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>1707230000</v>
+        <v>114852670000</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (111071)</t>
+          <t>BPN OKUT (669055)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>BPN OKUT</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2468,24 +2468,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
@@ -2497,13 +2497,13 @@
         <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>48.71</v>
       </c>
       <c r="L18" t="n">
         <v>100</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>100</v>
@@ -2512,27 +2512,27 @@
         <v>100</v>
       </c>
       <c r="P18" t="n">
-        <v>100</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U18" t="n">
         <v>2026</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2541,16 +2541,16 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>53136840000</v>
+        <v>106528210000</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2559,24 +2559,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>KPP BATURAJA (410574)</t>
+          <t>RUTAN BATURAJA (692339)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>KPP BATURAJA</t>
+          <t>RUTAN BATURAJA</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2585,24 +2585,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>403409</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>100</v>
@@ -2611,45 +2611,45 @@
         <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>100</v>
+        <v>88.58</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>61.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>87.75</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U19" t="n">
         <v>2026</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2658,42 +2658,42 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>1376500000</v>
+        <v>405581540000</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (403409)</t>
+          <t>PUSLATPUR AD (685001)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>PUSLATPUR AD</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2702,24 +2702,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>006</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>402268</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>86.45</v>
       </c>
       <c r="G20" t="n">
-        <v>100</v>
+        <v>83.64</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
@@ -2728,45 +2728,45 @@
         <v>100</v>
       </c>
       <c r="J20" t="n">
-        <v>100</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>67.27</v>
       </c>
       <c r="L20" t="n">
         <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>100</v>
+        <v>69.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U20" t="n">
         <v>2026</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2775,42 +2775,42 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>1230000000</v>
+        <v>14214110000</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402268)</t>
+          <t>KEJARI OKUS (007208)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KEJARI OKUS</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2819,24 +2819,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>100</v>
+        <v>72.72</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -2848,13 +2848,13 @@
         <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>100</v>
+        <v>45.44</v>
       </c>
       <c r="L21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>100</v>
@@ -2863,27 +2863,27 @@
         <v>100</v>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>69.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>86.36</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U21" t="n">
         <v>2026</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2892,42 +2892,42 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>42331120000</v>
+        <v>38902730000</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>PA BATURAJA (402267)</t>
+          <t>KPU OKU (656553)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>PA BATURAJA</t>
+          <t>KPU OKU</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2936,24 +2936,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>426050</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>94.37</v>
       </c>
       <c r="G22" t="n">
-        <v>100</v>
+        <v>76.84</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
@@ -2962,16 +2962,16 @@
         <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>100</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>53.67</v>
       </c>
       <c r="L22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>100</v>
@@ -2980,27 +2980,27 @@
         <v>100</v>
       </c>
       <c r="P22" t="n">
-        <v>100</v>
+        <v>69.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>86.31</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U22" t="n">
         <v>2026</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3009,35 +3009,35 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>64847500000</v>
+        <v>9098870000</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>PA MARTAPURA (401944)</t>
+          <t>MTSN 1 OKU (426050)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>PA MARTAPURA</t>
+          <t>MTSN 1 OKU</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -3053,24 +3053,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>418456</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>99.92</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
@@ -3082,7 +3082,7 @@
         <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>99.84</v>
+        <v>43.35</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="P23" t="n">
-        <v>79.97</v>
+        <v>68.67</v>
       </c>
       <c r="Q23" t="n">
         <v>80</v>
@@ -3106,18 +3106,18 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>99.95999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U23" t="n">
         <v>2026</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>67124350000</v>
+        <v>43471570000</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3144,17 +3144,17 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418456)</t>
+          <t>KPU OKUS (656574)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KPU OKUS</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
@@ -3170,24 +3170,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>076</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>99.87</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
@@ -3199,42 +3199,42 @@
         <v>100</v>
       </c>
       <c r="K24" t="n">
-        <v>99.73999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="L24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>99.75</v>
+        <v>100</v>
       </c>
       <c r="O24" t="n">
         <v>100</v>
       </c>
       <c r="P24" t="n">
-        <v>99.92</v>
+        <v>68.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>99.92</v>
+        <v>85.8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U24" t="n">
         <v>2026</v>
       </c>
       <c r="V24" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3243,16 +3243,16 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>18312800000</v>
+        <v>39931940000</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3261,17 +3261,17 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>KEJARI  OKU (007130)</t>
+          <t>KPU OKUT (656560)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>KEJARI  OKU</t>
+          <t>KPU OKUT</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
@@ -3287,24 +3287,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>99.81999999999999</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
@@ -3316,7 +3316,7 @@
         <v>100</v>
       </c>
       <c r="K25" t="n">
-        <v>99.63</v>
+        <v>39.85</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>100</v>
       </c>
       <c r="P25" t="n">
-        <v>79.93000000000001</v>
+        <v>67.97</v>
       </c>
       <c r="Q25" t="n">
         <v>80</v>
@@ -3340,18 +3340,18 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>99.91</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U25" t="n">
         <v>2026</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3360,35 +3360,35 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>43471570000</v>
+        <v>38391890000</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>KPU OKUS (656574)</t>
+          <t>BPS OKUS (667215)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>KPU OKUS</t>
+          <t>BPS OKUS</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr"/>
@@ -3404,24 +3404,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>024</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>99.72</v>
+        <v>76.11</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
@@ -3433,10 +3433,10 @@
         <v>100</v>
       </c>
       <c r="K26" t="n">
-        <v>99.44</v>
+        <v>28.33</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3448,27 +3448,27 @@
         <v>100</v>
       </c>
       <c r="P26" t="n">
-        <v>79.89</v>
+        <v>75.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>99.86</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U26" t="n">
         <v>2026</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3477,16 +3477,16 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>38902730000</v>
+        <v>14555550000</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3495,17 +3495,17 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KPU OKU (656553)</t>
+          <t>LOKA LABKESMAS (690801)</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KPU OKU</t>
+          <t>LOKA LABKESMAS</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>97.44</v>
       </c>
       <c r="G27" t="n">
-        <v>99.63</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -3547,10 +3547,10 @@
         <v>100</v>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>94.88</v>
       </c>
       <c r="K27" t="n">
-        <v>99.48999999999999</v>
+        <v>39.29</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>99.77</v>
+        <v>100</v>
       </c>
       <c r="O27" t="n">
         <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>79.88</v>
+        <v>67.09</v>
       </c>
       <c r="Q27" t="n">
         <v>80</v>
@@ -3574,18 +3574,18 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>99.84</v>
+        <v>83.86</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U27" t="n">
         <v>2026</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z27" t="n">
@@ -3638,27 +3638,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>403410</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>75.44</v>
       </c>
       <c r="H28" t="n">
-        <v>98.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
@@ -3667,42 +3667,42 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>26.32</v>
       </c>
       <c r="L28" t="n">
         <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>98.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>99.67</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>99.67</v>
+        <v>83.63</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U28" t="n">
         <v>2026</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3711,35 +3711,35 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>729500000</v>
+        <v>53136840000</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>PA  MUARADUA (403410)</t>
+          <t>KPP BATURAJA (410574)</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>PA  MUARADUA</t>
+          <t>KPP BATURAJA</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr"/>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>99.48</v>
+        <v>66.75</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -3784,13 +3784,13 @@
         <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>97.92</v>
+        <v>33.49</v>
       </c>
       <c r="L29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
@@ -3799,27 +3799,27 @@
         <v>100</v>
       </c>
       <c r="P29" t="n">
-        <v>99.58</v>
+        <v>66.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>99.58</v>
+        <v>83.37</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U29" t="n">
         <v>2026</v>
       </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>105914680000</v>
+        <v>61767300000</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3846,17 +3846,17 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA (692334)</t>
+          <t>BPS OKUT (668529)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>LAPAS MUARA DUA</t>
+          <t>BPS OKUT</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr"/>
@@ -3872,24 +3872,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>054</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>418458</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>90.97</v>
       </c>
       <c r="G30" t="n">
-        <v>99.31999999999999</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -3898,45 +3898,45 @@
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>81.94</v>
       </c>
       <c r="K30" t="n">
-        <v>97.28</v>
+        <v>45.63</v>
       </c>
       <c r="L30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>99.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="O30" t="n">
         <v>100</v>
       </c>
       <c r="P30" t="n">
-        <v>99.45999999999999</v>
+        <v>66.42</v>
       </c>
       <c r="Q30" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>99.45999999999999</v>
+        <v>83.02</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U30" t="n">
         <v>2026</v>
       </c>
       <c r="V30" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3945,35 +3945,35 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>9346940000</v>
+        <v>37327090000</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418458)</t>
+          <t>BPS OKU (428258)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>BPS OKU</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr"/>
@@ -3989,24 +3989,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>056</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>597558</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>85.83</v>
       </c>
       <c r="G31" t="n">
-        <v>98.40000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
@@ -4015,10 +4015,10 @@
         <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>100</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>96.8</v>
+        <v>50.35</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>79.36</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="Q31" t="n">
         <v>80</v>
@@ -4042,18 +4042,18 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>99.2</v>
+        <v>82.27</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U31" t="n">
         <v>2026</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4062,35 +4062,35 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>3898470000</v>
+        <v>50054370000</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS (597558)</t>
+          <t>BPN OKUS (670561)</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>MAN 2 OKUS</t>
+          <t>BPN OKUS</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr"/>
@@ -4106,24 +4106,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>440505</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>96.92</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>99.98</v>
+        <v>60.11</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
@@ -4132,10 +4132,10 @@
         <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>93.83</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>99.95</v>
+        <v>20.22</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="P32" t="n">
-        <v>79.06</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="Q32" t="n">
         <v>80</v>
@@ -4159,18 +4159,18 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>98.83</v>
+        <v>80.06</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U32" t="n">
         <v>2026</v>
       </c>
       <c r="V32" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4179,35 +4179,35 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>39931940000</v>
+        <v>1001460000</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>KPU OKUT (656560)</t>
+          <t>KEMENAG OKUS (440505)</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>KPU OKUT</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr"/>
@@ -4223,24 +4223,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>597558</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>98.45999999999999</v>
+        <v>59.74</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
@@ -4252,13 +4252,13 @@
         <v>100</v>
       </c>
       <c r="K33" t="n">
-        <v>93.84</v>
+        <v>19.48</v>
       </c>
       <c r="L33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>100</v>
@@ -4267,27 +4267,27 @@
         <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>98.77</v>
+        <v>63.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>98.77</v>
+        <v>79.87</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U33" t="n">
         <v>2026</v>
       </c>
       <c r="V33" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4296,35 +4296,35 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>14555550000</v>
+        <v>3898470000</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS (690801)</t>
+          <t>MAN 2 OKUS (597558)</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>LOKA LABKESMAS</t>
+          <t>MAN 2 OKUS</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr"/>
@@ -4340,24 +4340,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>015</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>96.09</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>55.76</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -4366,10 +4366,10 @@
         <v>100</v>
       </c>
       <c r="J34" t="n">
-        <v>92.17</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>11.52</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         <v>100</v>
       </c>
       <c r="P34" t="n">
-        <v>78.83</v>
+        <v>62.3</v>
       </c>
       <c r="Q34" t="n">
         <v>80</v>
@@ -4393,18 +4393,18 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>98.53</v>
+        <v>77.88</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U34" t="n">
         <v>2026</v>
       </c>
       <c r="V34" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4413,35 +4413,35 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>10675360000</v>
+        <v>11480750000</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>BNN OKUT (111079)</t>
+          <t>KPPN BATURAJA (527975)</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>BNN OKUT</t>
+          <t>KPPN BATURAJA</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr"/>
@@ -4474,7 +4474,7 @@
         <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>98.14</v>
+        <v>55.33</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -4486,13 +4486,13 @@
         <v>100</v>
       </c>
       <c r="K35" t="n">
-        <v>92.56999999999999</v>
+        <v>10.66</v>
       </c>
       <c r="L35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>100</v>
@@ -4501,27 +4501,27 @@
         <v>100</v>
       </c>
       <c r="P35" t="n">
-        <v>98.51000000000001</v>
+        <v>62.13</v>
       </c>
       <c r="Q35" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>98.51000000000001</v>
+        <v>77.67</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U35" t="n">
         <v>2026</v>
       </c>
       <c r="V35" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z35" t="n">
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>94.89</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>100</v>
+        <v>68.25</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
@@ -4600,16 +4600,16 @@
         <v>100</v>
       </c>
       <c r="J36" t="n">
-        <v>89.78</v>
+        <v>63.48</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>36.5</v>
       </c>
       <c r="L36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>100</v>
@@ -4618,27 +4618,27 @@
         <v>100</v>
       </c>
       <c r="P36" t="n">
-        <v>98.47</v>
+        <v>61.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>98.47</v>
+        <v>77.28</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U36" t="n">
         <v>2026</v>
       </c>
       <c r="V36" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z36" t="n">
@@ -4691,24 +4691,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>418458</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>94.28</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>100</v>
+        <v>52.06</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -4717,16 +4717,16 @@
         <v>100</v>
       </c>
       <c r="J37" t="n">
-        <v>88.56</v>
+        <v>100</v>
       </c>
       <c r="K37" t="n">
-        <v>100</v>
+        <v>4.11</v>
       </c>
       <c r="L37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>100</v>
@@ -4735,27 +4735,27 @@
         <v>100</v>
       </c>
       <c r="P37" t="n">
-        <v>98.28</v>
+        <v>60.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>98.28</v>
+        <v>76.03</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U37" t="n">
         <v>2026</v>
       </c>
       <c r="V37" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4764,35 +4764,35 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>128489370000</v>
+        <v>9346940000</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>PN BATURAJA (098963)</t>
+          <t>KEMENAG OKU (418458)</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>PN BATURAJA</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr"/>
@@ -4813,19 +4813,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>418459</t>
+          <t>553792</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>96.36</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
@@ -4834,10 +4834,10 @@
         <v>100</v>
       </c>
       <c r="J38" t="n">
-        <v>100</v>
+        <v>51.01</v>
       </c>
       <c r="K38" t="n">
-        <v>92.70999999999999</v>
+        <v>40.51</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="P38" t="n">
-        <v>78.54000000000001</v>
+        <v>60.75</v>
       </c>
       <c r="Q38" t="n">
         <v>80</v>
@@ -4861,18 +4861,18 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>98.18000000000001</v>
+        <v>75.94</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U38" t="n">
         <v>2026</v>
       </c>
       <c r="V38" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4881,16 +4881,16 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>1731600000</v>
+        <v>9731020000</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -4899,17 +4899,17 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418459)</t>
+          <t>MTSN 1 OKUS (553792)</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>MTSN 1 OKUS</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr"/>
@@ -4930,19 +4930,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>426050</t>
+          <t>418457</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>94.25</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>99.66</v>
+        <v>51.36</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
@@ -4951,16 +4951,16 @@
         <v>100</v>
       </c>
       <c r="J39" t="n">
-        <v>88.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
-        <v>98.62</v>
+        <v>2.71</v>
       </c>
       <c r="L39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>100</v>
@@ -4969,27 +4969,27 @@
         <v>100</v>
       </c>
       <c r="P39" t="n">
-        <v>98</v>
+        <v>60.54</v>
       </c>
       <c r="Q39" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>98</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U39" t="n">
         <v>2026</v>
       </c>
       <c r="V39" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4998,16 +4998,16 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>9098870000</v>
+        <v>7789580000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5016,17 +5016,17 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU (426050)</t>
+          <t>KEMENAG OKU (418457)</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>MTSN 1 OKU</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr"/>
@@ -5042,24 +5042,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>344894</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>92.62</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>99.47</v>
+        <v>50.62</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -5068,45 +5068,45 @@
         <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>85.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
-        <v>98.41</v>
+        <v>1.23</v>
       </c>
       <c r="L40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O40" t="n">
         <v>100</v>
       </c>
       <c r="P40" t="n">
-        <v>87.47</v>
+        <v>60.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>97.19</v>
+        <v>75.31</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U40" t="n">
         <v>2026</v>
       </c>
       <c r="V40" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5115,35 +5115,35 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>287629890000</v>
+        <v>5891850000</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR (344894)</t>
+          <t>MTSN 2 OKUS (418462)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>RUMKIT NOESMIR</t>
+          <t>MTSN 2 OKUS</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr"/>
@@ -5159,24 +5159,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="G41" t="n">
-        <v>98.52</v>
+        <v>50.22</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -5185,45 +5185,45 @@
         <v>100</v>
       </c>
       <c r="J41" t="n">
-        <v>84.98999999999999</v>
+        <v>100</v>
       </c>
       <c r="K41" t="n">
-        <v>99.88</v>
+        <v>0.44</v>
       </c>
       <c r="L41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>94.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="O41" t="n">
         <v>100</v>
       </c>
       <c r="P41" t="n">
-        <v>97.15000000000001</v>
+        <v>60.09</v>
       </c>
       <c r="Q41" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>97.15000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U41" t="n">
         <v>2026</v>
       </c>
       <c r="V41" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -5232,16 +5232,16 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>405581540000</v>
+        <v>90057130000</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -5250,17 +5250,17 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD (685001)</t>
+          <t>KEMENAG OKUS (440502)</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>PUSLATPUR AD</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr"/>
@@ -5281,19 +5281,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>666503</t>
+          <t>418456</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>92.8</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>99.04000000000001</v>
+        <v>50.19</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -5302,16 +5302,16 @@
         <v>100</v>
       </c>
       <c r="J42" t="n">
-        <v>85.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
-        <v>96.15000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="L42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>100</v>
@@ -5320,27 +5320,27 @@
         <v>100</v>
       </c>
       <c r="P42" t="n">
-        <v>97.06999999999999</v>
+        <v>60.07</v>
       </c>
       <c r="Q42" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>97.06999999999999</v>
+        <v>75.09</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U42" t="n">
         <v>2026</v>
       </c>
       <c r="V42" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5349,35 +5349,35 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>16133240000</v>
+        <v>67124350000</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666503)</t>
+          <t>KEMENAG OKU (418456)</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr"/>
@@ -5393,24 +5393,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>666501</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>92.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="G43" t="n">
-        <v>99.18000000000001</v>
+        <v>50.04</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
@@ -5419,16 +5419,16 @@
         <v>100</v>
       </c>
       <c r="J43" t="n">
-        <v>84.84999999999999</v>
+        <v>100</v>
       </c>
       <c r="K43" t="n">
-        <v>96.72</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
@@ -5437,27 +5437,27 @@
         <v>100</v>
       </c>
       <c r="P43" t="n">
-        <v>97.06999999999999</v>
+        <v>60.01</v>
       </c>
       <c r="Q43" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>97.06999999999999</v>
+        <v>75.02</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U43" t="n">
         <v>2026</v>
       </c>
       <c r="V43" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5466,42 +5466,42 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>14214110000</v>
+        <v>142639230000</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>KEJARI OKUS (007208)</t>
+          <t>KEMENAG OKUT (666501)</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>KEJARI OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5510,24 +5510,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>401945</t>
+          <t>440506</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MUARADUA</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>89.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>99.92</v>
+        <v>50</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
@@ -5536,16 +5536,16 @@
         <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>78.8</v>
+        <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>99.66</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>100</v>
@@ -5554,27 +5554,27 @@
         <v>100</v>
       </c>
       <c r="P44" t="n">
-        <v>96.75</v>
+        <v>60</v>
       </c>
       <c r="Q44" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>96.75</v>
+        <v>75</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U44" t="n">
         <v>2026</v>
       </c>
       <c r="V44" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5583,42 +5583,42 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>40484710000</v>
+        <v>970430000</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>PA MUARADUA (401945)</t>
+          <t>KEMENAG OKUS (440506)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>PA MUARADUA</t>
+          <t>KEMENAG OKUS</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5627,24 +5627,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>402268</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>89.62</v>
+        <v>100</v>
       </c>
       <c r="G45" t="n">
-        <v>98.31</v>
+        <v>50</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
@@ -5653,45 +5653,45 @@
         <v>100</v>
       </c>
       <c r="J45" t="n">
-        <v>79.23</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
-        <v>99.91</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>100</v>
       </c>
       <c r="P45" t="n">
-        <v>96.2</v>
+        <v>60</v>
       </c>
       <c r="Q45" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>96.2</v>
+        <v>75</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U45" t="n">
         <v>2026</v>
       </c>
       <c r="V45" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5700,35 +5700,35 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>15177700000</v>
+        <v>1230000000</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>MAN 1 OKU (424245)</t>
+          <t>PA BATURAJA (402268)</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>MAN 1 OKU</t>
+          <t>PA BATURAJA</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr"/>
@@ -5744,24 +5744,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>686503</t>
+          <t>424967</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>88.25</v>
+        <v>94.59</v>
       </c>
       <c r="G46" t="n">
-        <v>99.54000000000001</v>
+        <v>50.27</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
@@ -5770,45 +5770,45 @@
         <v>100</v>
       </c>
       <c r="J46" t="n">
-        <v>76.48999999999999</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>98.17</v>
+        <v>0.54</v>
       </c>
       <c r="L46" t="n">
         <v>100</v>
       </c>
       <c r="M46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>100</v>
       </c>
       <c r="P46" t="n">
-        <v>96.11</v>
+        <v>58.49</v>
       </c>
       <c r="Q46" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>96.11</v>
+        <v>73.11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U46" t="n">
         <v>2026</v>
       </c>
       <c r="V46" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5817,16 +5817,16 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>31225620000</v>
+        <v>13427580000</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -5835,17 +5835,17 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS (686503)</t>
+          <t>MTSN 1 OKUT (424967)</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>BAWASLU OKUS</t>
+          <t>MTSN 1 OKUT</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr"/>
@@ -5861,24 +5861,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>87.98</v>
       </c>
       <c r="G47" t="n">
-        <v>95.08</v>
+        <v>55.09</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
@@ -5887,16 +5887,16 @@
         <v>100</v>
       </c>
       <c r="J47" t="n">
-        <v>100</v>
+        <v>75.95</v>
       </c>
       <c r="K47" t="n">
-        <v>80.3</v>
+        <v>10.18</v>
       </c>
       <c r="L47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>100</v>
@@ -5905,27 +5905,27 @@
         <v>100</v>
       </c>
       <c r="P47" t="n">
-        <v>96.06</v>
+        <v>58.43</v>
       </c>
       <c r="Q47" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>96.06</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U47" t="n">
         <v>2026</v>
       </c>
       <c r="V47" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5934,16 +5934,16 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>38391890000</v>
+        <v>15177700000</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -5952,17 +5952,17 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>BPS OKUS (667215)</t>
+          <t>MAN 1 OKU (424245)</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>BPS OKUS</t>
+          <t>MAN 1 OKU</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr"/>
@@ -5978,24 +5978,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>686503</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>88.22</v>
+        <v>67.13</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
@@ -6004,10 +6004,10 @@
         <v>100</v>
       </c>
       <c r="J48" t="n">
-        <v>76.43000000000001</v>
+        <v>34.25</v>
       </c>
       <c r="K48" t="n">
-        <v>100</v>
+        <v>41.01</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="P48" t="n">
-        <v>76.45999999999999</v>
+        <v>58.34</v>
       </c>
       <c r="Q48" t="n">
         <v>80</v>
@@ -6031,18 +6031,18 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>95.58</v>
+        <v>72.92</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U48" t="n">
         <v>2026</v>
       </c>
       <c r="V48" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6051,35 +6051,35 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>5176090000</v>
+        <v>31225620000</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT (553099)</t>
+          <t>BAWASLU OKUS (686503)</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUT</t>
+          <t>BAWASLU OKUS</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr"/>
@@ -6095,24 +6095,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>426066</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>88.09999999999999</v>
+        <v>80.69</v>
       </c>
       <c r="G49" t="n">
-        <v>98.65000000000001</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
@@ -6121,16 +6121,16 @@
         <v>100</v>
       </c>
       <c r="J49" t="n">
-        <v>76.2</v>
+        <v>61.37</v>
       </c>
       <c r="K49" t="n">
-        <v>94.61</v>
+        <v>4.86</v>
       </c>
       <c r="L49" t="n">
         <v>100</v>
       </c>
       <c r="M49" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>100</v>
@@ -6139,27 +6139,27 @@
         <v>100</v>
       </c>
       <c r="P49" t="n">
-        <v>95.34999999999999</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="Q49" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>95.34999999999999</v>
+        <v>72.42</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U49" t="n">
         <v>2026</v>
       </c>
       <c r="V49" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -6168,35 +6168,35 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>74397990000</v>
+        <v>20589110000</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>BPN OKU (431142)</t>
+          <t>MAN 1 OKUT (426066)</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>BPN OKU</t>
+          <t>MAN 1 OKUT</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr"/>
@@ -6212,24 +6212,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>666502</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>96.73</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>95.2</v>
+        <v>0.36</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
@@ -6238,45 +6238,45 @@
         <v>100</v>
       </c>
       <c r="J50" t="n">
-        <v>93.45</v>
+        <v>100</v>
       </c>
       <c r="K50" t="n">
-        <v>80.81</v>
+        <v>0.36</v>
       </c>
       <c r="L50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>100</v>
       </c>
       <c r="P50" t="n">
-        <v>95.18000000000001</v>
+        <v>50.07</v>
       </c>
       <c r="Q50" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>95.18000000000001</v>
+        <v>71.53</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U50" t="n">
         <v>2026</v>
       </c>
       <c r="V50" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -6285,16 +6285,16 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>37327090000</v>
+        <v>15707450000</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -6303,17 +6303,17 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>BPS OKU (428258)</t>
+          <t>KEMENAG OKUT (666502)</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>BPS OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr"/>
@@ -6329,24 +6329,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>670561</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>95.89</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>93.37</v>
+        <v>0.33</v>
       </c>
       <c r="H51" t="n">
         <v>100</v>
@@ -6355,10 +6355,10 @@
         <v>100</v>
       </c>
       <c r="J51" t="n">
-        <v>91.78</v>
+        <v>100</v>
       </c>
       <c r="K51" t="n">
-        <v>86.73999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -6367,33 +6367,33 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>100</v>
       </c>
       <c r="P51" t="n">
-        <v>76.12</v>
+        <v>50.07</v>
       </c>
       <c r="Q51" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>95.14</v>
+        <v>71.52</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U51" t="n">
         <v>2026</v>
       </c>
       <c r="V51" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6402,42 +6402,42 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>50054370000</v>
+        <v>7585360000</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>BPN OKUS (670561)</t>
+          <t>MTSN 3 OKUS (574370)</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>BPN OKUS</t>
+          <t>MTSN 3 OKUS</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6451,19 +6451,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>418457</t>
+          <t>666505</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>93.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="G52" t="n">
-        <v>93.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>100</v>
@@ -6472,10 +6472,10 @@
         <v>100</v>
       </c>
       <c r="J52" t="n">
-        <v>87.36</v>
+        <v>100</v>
       </c>
       <c r="K52" t="n">
-        <v>87.42</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6484,33 +6484,33 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>100</v>
       </c>
       <c r="P52" t="n">
-        <v>75.59</v>
+        <v>50</v>
       </c>
       <c r="Q52" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>94.48999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U52" t="n">
         <v>2026</v>
       </c>
       <c r="V52" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6519,16 +6519,16 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>7789580000</v>
+        <v>600000000</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -6537,24 +6537,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU (418457)</t>
+          <t>KEMENAG OKUT (666505)</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>KEMENAG OKU</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6563,24 +6563,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>666504</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>92.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
@@ -6592,42 +6592,42 @@
         <v>100</v>
       </c>
       <c r="K53" t="n">
-        <v>69.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>100</v>
       </c>
       <c r="P53" t="n">
-        <v>93.92</v>
+        <v>50</v>
       </c>
       <c r="Q53" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>93.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U53" t="n">
         <v>2026</v>
       </c>
       <c r="V53" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6636,42 +6636,42 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>61767300000</v>
+        <v>3127760000</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>BPS OKUT (668529)</t>
+          <t>KEMENAG OKUT (666504)</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>BPS OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6685,19 +6685,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>424967</t>
+          <t>418459</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>87.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>96.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -6706,45 +6706,45 @@
         <v>100</v>
       </c>
       <c r="J54" t="n">
-        <v>75.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="K54" t="n">
-        <v>84.61</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>100</v>
       </c>
       <c r="P54" t="n">
-        <v>93.22</v>
+        <v>50</v>
       </c>
       <c r="Q54" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>93.22</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U54" t="n">
         <v>2026</v>
       </c>
       <c r="V54" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6753,42 +6753,42 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>13427580000</v>
+        <v>1731600000</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT (424967)</t>
+          <t>KEMENAG OKU (418459)</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUT</t>
+          <t>KEMENAG OKU</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6802,19 +6802,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>553792</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>82.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>99.05</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
@@ -6823,10 +6823,10 @@
         <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>65.42</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
-        <v>98.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -6835,33 +6835,33 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>100</v>
       </c>
       <c r="P55" t="n">
-        <v>74.43000000000001</v>
+        <v>50</v>
       </c>
       <c r="Q55" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>93.04000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U55" t="n">
         <v>2026</v>
       </c>
       <c r="V55" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -6870,16 +6870,16 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>9731020000</v>
+        <v>1707230000</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -6888,17 +6888,17 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS (553792)</t>
+          <t>KEMENAG OKUT (111071)</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>MTSN 1 OKUS</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr"/>
@@ -6914,24 +6914,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>426066</t>
+          <t>419006</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU TIMUR</t>
+          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>86.23999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>95.86</v>
+        <v>38.84</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
@@ -6940,45 +6940,45 @@
         <v>100</v>
       </c>
       <c r="J56" t="n">
-        <v>72.48</v>
+        <v>37.79</v>
       </c>
       <c r="K56" t="n">
-        <v>83.44</v>
+        <v>38.84</v>
       </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>100</v>
       </c>
       <c r="P56" t="n">
-        <v>92.56</v>
+        <v>48.44</v>
       </c>
       <c r="Q56" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>92.56</v>
+        <v>69.2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U56" t="n">
         <v>2026</v>
       </c>
       <c r="V56" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6987,16 +6987,16 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>20589110000</v>
+        <v>29335310000</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -7005,17 +7005,17 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT (426066)</t>
+          <t>BAWASLU OKU (419006)</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>MAN 1 OKUT</t>
+          <t>BAWASLU OKU</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr"/>
@@ -7031,24 +7031,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>012</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>666502</t>
+          <t>344894</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
+          <t>RUMKIT TK. III 02.06.02 DR. NOESMIR BATURAJA KESDAM II/SWJ</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>64.7</v>
       </c>
       <c r="G57" t="n">
-        <v>84.53</v>
+        <v>29.05</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -7057,10 +7057,10 @@
         <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>100</v>
+        <v>29.4</v>
       </c>
       <c r="K57" t="n">
-        <v>69.05</v>
+        <v>29.05</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7069,33 +7069,33 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>100</v>
       </c>
       <c r="P57" t="n">
-        <v>73.81</v>
+        <v>45.22</v>
       </c>
       <c r="Q57" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>92.26000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U57" t="n">
         <v>2026</v>
       </c>
       <c r="V57" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -7104,35 +7104,35 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>15707450000</v>
+        <v>287629890000</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>BESAR</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT (666502)</t>
+          <t>RUMKIT NOESMIR (344894)</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>KEMENAG OKUT</t>
+          <t>RUMKIT NOESMIR</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr"/>
@@ -7153,19 +7153,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>661192</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>85.63</v>
+        <v>50.75</v>
       </c>
       <c r="G58" t="n">
-        <v>94.89</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
@@ -7174,13 +7174,13 @@
         <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>71.26000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="K58" t="n">
-        <v>89.77</v>
+        <v>0.55</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -7192,27 +7192,27 @@
         <v>100</v>
       </c>
       <c r="P58" t="n">
-        <v>73.64</v>
+        <v>55.33</v>
       </c>
       <c r="Q58" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>92.05</v>
+        <v>61.48</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U58" t="n">
         <v>2026</v>
       </c>
       <c r="V58" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -7221,16 +7221,16 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>5671610000</v>
+        <v>6368000000</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -7239,17 +7239,17 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS (661192)</t>
+          <t>MTSN 2 OKUT (418471)</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUS</t>
+          <t>MTSN 2 OKUT</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr"/>
@@ -7265,24 +7265,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>056</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>669055</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KANTOR PERTANAHAN KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>94.68000000000001</v>
+        <v>50.34</v>
       </c>
       <c r="G59" t="n">
-        <v>91.95999999999999</v>
+        <v>66.78</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
@@ -7291,16 +7291,16 @@
         <v>100</v>
       </c>
       <c r="J59" t="n">
-        <v>89.36</v>
+        <v>0.68</v>
       </c>
       <c r="K59" t="n">
-        <v>67.84</v>
+        <v>0.33</v>
       </c>
       <c r="L59" t="n">
         <v>100</v>
       </c>
       <c r="M59" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>100</v>
@@ -7309,27 +7309,27 @@
         <v>100</v>
       </c>
       <c r="P59" t="n">
-        <v>91.97</v>
+        <v>55.17</v>
       </c>
       <c r="Q59" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>91.97</v>
+        <v>61.3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U59" t="n">
         <v>2026</v>
       </c>
       <c r="V59" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -7338,35 +7338,35 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>114852670000</v>
+        <v>4481070000</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>BESAR</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>BPN OKUT (669055)</t>
+          <t>MTSN 4 OKUT (597480)</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>BPN OKUT</t>
+          <t>MTSN 4 OKUT</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr"/>
@@ -7387,19 +7387,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>666503</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN AGAMA OKU TIMUR</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>84.84</v>
+        <v>56.83</v>
       </c>
       <c r="G60" t="n">
-        <v>94.43000000000001</v>
+        <v>54.07</v>
       </c>
       <c r="H60" t="n">
         <v>100</v>
@@ -7408,45 +7408,45 @@
         <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>69.67</v>
+        <v>13.66</v>
       </c>
       <c r="K60" t="n">
-        <v>77.98</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>99.72</v>
+        <v>100</v>
       </c>
       <c r="O60" t="n">
         <v>100</v>
       </c>
       <c r="P60" t="n">
-        <v>91.02</v>
+        <v>48.68</v>
       </c>
       <c r="Q60" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>91.02</v>
+        <v>60.85</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U60" t="n">
         <v>2026</v>
       </c>
       <c r="V60" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -7455,35 +7455,35 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>4481070000</v>
+        <v>16133240000</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>KECIL</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT (597480)</t>
+          <t>KEMENAG OKUT (666503)</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>MTSN 4 OKUT</t>
+          <t>KEMENAG OKUT</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr"/>
@@ -7504,31 +7504,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>79.63</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>93.34999999999999</v>
+        <v>56.22</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>67.94</v>
       </c>
       <c r="I61" t="n">
         <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>59.26</v>
+        <v>34.02</v>
       </c>
       <c r="K61" t="n">
-        <v>86.69</v>
+        <v>12.43</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -7540,10 +7540,10 @@
         <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>100</v>
+        <v>67.94</v>
       </c>
       <c r="P61" t="n">
-        <v>71.23</v>
+        <v>44.57</v>
       </c>
       <c r="Q61" t="n">
         <v>80</v>
@@ -7552,18 +7552,18 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>89.03</v>
+        <v>55.72</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U61" t="n">
         <v>2026</v>
       </c>
       <c r="V61" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>7585360000</v>
+        <v>5176090000</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -7590,17 +7590,17 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS (574370)</t>
+          <t>MTSN 3 OKUT (553099)</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>MTSN 3 OKUS</t>
+          <t>MTSN 3 OKUT</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr"/>
@@ -7616,51 +7616,51 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>662127</t>
+          <t>403410</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MUARADUA</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>71.36</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>99.48</v>
+        <v>50</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I62" t="n">
         <v>100</v>
       </c>
       <c r="J62" t="n">
-        <v>42.72</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>98.95</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="P62" t="n">
-        <v>71.2</v>
+        <v>42.5</v>
       </c>
       <c r="Q62" t="n">
         <v>80</v>
@@ -7669,18 +7669,18 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>89</v>
+        <v>53.13</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U62" t="n">
         <v>2026</v>
       </c>
       <c r="V62" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -7689,35 +7689,35 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>13489830000</v>
+        <v>729500000</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>SEDANG</t>
+          <t>KECIL</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS (662127)</t>
+          <t>PA  MUARADUA (403410)</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>MAN 1 OKUS</t>
+          <t>PA  MUARADUA</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr"/>
@@ -7747,57 +7747,57 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>72.23</v>
+        <v>50</v>
       </c>
       <c r="G63" t="n">
-        <v>96.34</v>
+        <v>100</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>100</v>
       </c>
       <c r="J63" t="n">
-        <v>44.45</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>85.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="L63" t="n">
         <v>100</v>
       </c>
       <c r="M63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>88.73999999999999</v>
+        <v>40</v>
       </c>
       <c r="Q63" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>88.73999999999999</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U63" t="n">
         <v>2026</v>
       </c>
       <c r="V63" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z63" t="n">
@@ -7850,71 +7850,71 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>695184</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 2 OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>79.62</v>
+        <v>50</v>
       </c>
       <c r="G64" t="n">
-        <v>90.36</v>
+        <v>100</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>100</v>
       </c>
       <c r="J64" t="n">
-        <v>59.23</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>81.44</v>
+        <v>100</v>
       </c>
       <c r="L64" t="n">
         <v>100</v>
       </c>
       <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q64" t="n">
         <v>80</v>
       </c>
-      <c r="N64" t="n">
-        <v>100</v>
-      </c>
-      <c r="O64" t="n">
-        <v>100</v>
-      </c>
-      <c r="P64" t="n">
-        <v>88.17</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>100</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>88.17</v>
+        <v>50</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U64" t="n">
         <v>2026</v>
       </c>
       <c r="V64" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -7923,16 +7923,16 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>6368000000</v>
+        <v>6722660000</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT (418471)</t>
+          <t>KANTOR KEMENHAJ OKUS (695184)</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>MTSN 2 OKUT</t>
+          <t>KANTOR KEMENHAJ OKUS</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr"/>
@@ -7967,71 +7967,71 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>695182</t>
+          <t>661192</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 4 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>76.69</v>
+        <v>54.04</v>
       </c>
       <c r="G65" t="n">
-        <v>92.92</v>
+        <v>51.27</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
       </c>
       <c r="J65" t="n">
-        <v>53.38</v>
+        <v>8.07</v>
       </c>
       <c r="K65" t="n">
-        <v>71.68000000000001</v>
+        <v>2.53</v>
       </c>
       <c r="L65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>100</v>
       </c>
       <c r="O65" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P65" t="n">
-        <v>87.34</v>
+        <v>37.97</v>
       </c>
       <c r="Q65" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>87.34</v>
+        <v>47.46</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U65" t="n">
         <v>2026</v>
       </c>
       <c r="V65" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -8040,16 +8040,16 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>6314270000</v>
+        <v>5671610000</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8058,17 +8058,17 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUT (695182)</t>
+          <t>MTSN 4 OKUS (661192)</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUT</t>
+          <t>MTSN 4 OKUS</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr"/>
@@ -8089,66 +8089,66 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>695184</t>
+          <t>695182</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR KEMENTERIAN HAJI DAN UMRAH KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>75.98</v>
+        <v>50</v>
       </c>
       <c r="G66" t="n">
-        <v>88.78</v>
+        <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>51.95</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>88.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="L66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>87.15000000000001</v>
+        <v>30</v>
       </c>
       <c r="Q66" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>87.15000000000001</v>
+        <v>42.86</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U66" t="n">
         <v>2026</v>
       </c>
       <c r="V66" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -8157,16 +8157,16 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>6722660000</v>
+        <v>6314270000</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8175,17 +8175,17 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS</t>
+          <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS (695184)</t>
+          <t>KANTOR KEMENHAJ OKUT (695182)</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>KANTOR KEMENHAJ OKUS</t>
+          <t>KANTOR KEMENHAJ OKUT</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr"/>
@@ -8201,71 +8201,71 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>419006</t>
+          <t>662127</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SEKRETARIAT BAWASLU KABUPATEN OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>79.72</v>
+        <v>50.65</v>
       </c>
       <c r="G67" t="n">
-        <v>72.90000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I67" t="n">
         <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>59.43</v>
+        <v>1.29</v>
       </c>
       <c r="K67" t="n">
-        <v>91.58</v>
+        <v>0.57</v>
       </c>
       <c r="L67" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P67" t="n">
-        <v>82.23</v>
+        <v>26.56</v>
       </c>
       <c r="Q67" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>82.23</v>
+        <v>37.94</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>JUNI</t>
+          <t>JANUARI</t>
         </is>
       </c>
       <c r="U67" t="n">
         <v>2026</v>
       </c>
       <c r="V67" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -8274,16 +8274,16 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>JUNI 2026</t>
+          <t>JANUARI 2026</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>29335310000</v>
+        <v>13489830000</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -8292,17 +8292,17 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>BAWASLU OKU (419006)</t>
+          <t>MAN 1 OKUS (662127)</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>BAWASLU OKU</t>
+          <t>MAN 1 OKUS</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr"/>
